--- a/data/trans_dic/P42C_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P42C_R-Estudios-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -516,39 +516,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya última consulta ginecológica fue en un centro privado</t>
+          <t>Población cuya última consulta ginecológica fue en un centro privado (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -579,21 +569,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -608,9 +583,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -625,17 +597,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,21 +621,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6,26%</t>
         </is>
@@ -678,47 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,71; 14,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,25; 5,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,62; 8,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 15,08</t>
+          <t>10,71; 14,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,59</t>
+          <t>2,25; 5,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,89</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,88; 15,08</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2,32; 5,59</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4,56; 8,89</t>
+          <t>4,62; 8,76</t>
         </is>
       </c>
     </row>
@@ -735,17 +677,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,21 +701,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,7%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>25,46%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>14,22%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>20,7%</t>
         </is>
@@ -788,47 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,22; 27,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,34; 15,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,33; 23,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,89; 28,09</t>
+          <t>23,22; 27,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,43; 16,09</t>
+          <t>12,34; 15,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,93; 23,42</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,89; 28,09</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12,43; 16,09</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16,93; 23,42</t>
+          <t>16,33; 23,36</t>
         </is>
       </c>
     </row>
@@ -845,17 +757,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,21 +781,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>48,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>45,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36,68%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>48,62%</t>
         </is>
@@ -898,47 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,74; 51,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,53; 41,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,31; 53,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40,65; 51,2</t>
+          <t>40,74; 51,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,56; 41,23</t>
+          <t>32,53; 41,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,05; 52,8</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>40,65; 51,2</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>32,56; 41,23</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>44,05; 52,8</t>
+          <t>44,31; 53,1</t>
         </is>
       </c>
     </row>
@@ -955,17 +837,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,21 +861,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,92%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15,48%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>23,16%</t>
         </is>
@@ -1008,47 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,16; 25,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,2; 16,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,75; 25,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,3; 25,65</t>
+          <t>22,16; 25,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,14; 16,91</t>
+          <t>14,2; 16,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,37; 25,12</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>22,3; 25,65</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14,14; 16,91</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20,37; 25,12</t>
+          <t>20,75; 25,22</t>
         </is>
       </c>
     </row>
@@ -1060,12 +912,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
@@ -1080,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1091,39 +942,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya última consulta ginecológica fue en un centro privado</t>
+          <t>Población cuya última consulta ginecológica fue en un centro privado (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1154,21 +995,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1183,9 +1009,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1200,17 +1023,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1224,21 +1047,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
@@ -1253,17 +1061,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123619</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24976</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27075</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1277,21 +1085,6 @@
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27075</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>123619</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24976</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>27075</t>
         </is>
@@ -1306,47 +1099,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>104039; 145313</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15602; 35742</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19987; 37914</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105636; 146425</t>
+          <t>104039; 145313</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16043; 38685</t>
+          <t>15602; 35742</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19715; 38467</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>105636; 146425</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>16043; 38685</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19715; 38467</t>
+          <t>19987; 37914</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1141,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>311</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>212</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>363</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1387,21 +1165,6 @@
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>363</t>
         </is>
@@ -1416,17 +1179,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346959</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>226350</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>243778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1440,21 +1203,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>243778</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>346959</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>226350</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>243778</t>
         </is>
@@ -1469,47 +1217,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>316378; 381250</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>196415; 254093</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>192355; 275078</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>311976; 382756</t>
+          <t>316378; 381250</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>197814; 256159</t>
+          <t>196415; 254093</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>199406; 275856</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>311976; 382756</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>197814; 256159</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>199406; 275856</t>
+          <t>192355; 275078</t>
         </is>
       </c>
     </row>
@@ -1526,17 +1259,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>169</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>299</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1550,21 +1283,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>299</t>
         </is>
@@ -1579,17 +1297,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184152</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>176779</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>195146</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1603,21 +1321,6 @@
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>195146</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>184152</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>176779</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>195146</t>
         </is>
@@ -1632,47 +1335,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>164224; 206794</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>156764; 198181</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>177835; 213119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>163862; 206405</t>
+          <t>164224; 206794</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>156926; 198690</t>
+          <t>156764; 198181</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>176799; 211935</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>163862; 206405</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>156926; 198690</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>176799; 211935</t>
+          <t>177835; 213119</t>
         </is>
       </c>
     </row>
@@ -1689,17 +1377,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>403</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1713,21 +1401,6 @@
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>709</t>
         </is>
@@ -1742,17 +1415,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>654730</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>428105</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>465999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1766,21 +1439,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>465999</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>654730</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>428105</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>465999</t>
         </is>
@@ -1795,47 +1453,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>606560; 699938</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>392731; 466845</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>417385; 507420</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>610321; 702000</t>
+          <t>606560; 699938</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>391241; 467917</t>
+          <t>392731; 466845</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>409851; 505398</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>610321; 702000</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>391241; 467917</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>409851; 505398</t>
+          <t>417385; 507420</t>
         </is>
       </c>
     </row>
@@ -1847,13 +1490,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/P42C_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P42C_R-Estudios-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,71; 14,96</t>
+          <t>10,62; 15,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,16</t>
+          <t>2,31; 5,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,76</t>
+          <t>4,62; 8,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,71; 14,96</t>
+          <t>10,62; 15,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,16</t>
+          <t>2,31; 5,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,76</t>
+          <t>4,62; 8,15</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,22; 27,98</t>
+          <t>23,12; 28,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,34; 15,96</t>
+          <t>12,57; 16,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,33; 23,36</t>
+          <t>20,47; 24,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,22; 27,98</t>
+          <t>23,12; 28,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,34; 15,96</t>
+          <t>12,57; 16,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,33; 23,36</t>
+          <t>20,47; 24,8</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,74; 51,3</t>
+          <t>40,68; 50,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,53; 41,12</t>
+          <t>32,29; 41,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,31; 53,1</t>
+          <t>43,46; 51,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40,74; 51,3</t>
+          <t>40,68; 50,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,53; 41,12</t>
+          <t>32,29; 41,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,31; 53,1</t>
+          <t>43,46; 51,6</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,16; 25,57</t>
+          <t>22,35; 25,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,2; 16,88</t>
+          <t>14,14; 16,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,75; 25,22</t>
+          <t>22,57; 25,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,16; 25,57</t>
+          <t>22,35; 25,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,2; 16,88</t>
+          <t>14,14; 16,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,75; 25,22</t>
+          <t>22,57; 25,87</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27075</t>
+          <t>28742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27075</t>
+          <t>28742</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>104039; 145313</t>
+          <t>103108; 146465</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15602; 35742</t>
+          <t>16012; 37391</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19987; 37914</t>
+          <t>21595; 38068</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104039; 145313</t>
+          <t>103108; 146465</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15602; 35742</t>
+          <t>16012; 37391</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19987; 37914</t>
+          <t>21595; 38068</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>243778</t>
+          <t>268747</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>243778</t>
+          <t>268747</t>
         </is>
       </c>
     </row>
@@ -1217,32 +1217,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>316378; 381250</t>
+          <t>315045; 382117</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>196415; 254093</t>
+          <t>200075; 256992</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>192355; 275078</t>
+          <t>244079; 295614</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>316378; 381250</t>
+          <t>315045; 382117</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>196415; 254093</t>
+          <t>200075; 256992</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>192355; 275078</t>
+          <t>244079; 295614</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195146</t>
+          <t>213974</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>195146</t>
+          <t>213974</t>
         </is>
       </c>
     </row>
@@ -1335,32 +1335,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>164224; 206794</t>
+          <t>164011; 204481</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>156764; 198181</t>
+          <t>155623; 199554</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>177835; 213119</t>
+          <t>194434; 230821</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>164224; 206794</t>
+          <t>164011; 204481</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>156764; 198181</t>
+          <t>155623; 199554</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>177835; 213119</t>
+          <t>194434; 230821</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>465999</t>
+          <t>511463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>465999</t>
+          <t>511463</t>
         </is>
       </c>
     </row>
@@ -1453,32 +1453,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>606560; 699938</t>
+          <t>611600; 705222</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>392731; 466845</t>
+          <t>391040; 467693</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>417385; 507420</t>
+          <t>475366; 544883</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>606560; 699938</t>
+          <t>611600; 705222</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>392731; 466845</t>
+          <t>391040; 467693</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>417385; 507420</t>
+          <t>475366; 544883</t>
         </is>
       </c>
     </row>
